--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9710F8DA-DDC0-488C-BFB8-DB874D1580D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFF6BA5-DDE0-4250-A4B0-54A8D4C42CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3990" yWindow="3945" windowWidth="17340" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -223,9 +223,6 @@
     <t>E266</t>
   </si>
   <si>
-    <t>O472</t>
-  </si>
-  <si>
     <t>coeqwal_GW_scenario_listing_v3.xlsx</t>
   </si>
   <si>
@@ -248,6 +245,9 @@
   </si>
   <si>
     <t>J101</t>
+  </si>
+  <si>
+    <t>O487</t>
   </si>
 </sst>
 </file>
@@ -585,14 +585,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="5" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="5" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -606,7 +606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -614,15 +614,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -630,7 +630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -641,10 +641,10 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -655,10 +655,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -669,10 +669,10 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -683,10 +683,10 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>61</v>
       </c>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -711,10 +711,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -725,10 +725,10 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -736,7 +736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -744,7 +744,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -752,7 +752,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -766,7 +766,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -774,7 +774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -782,7 +782,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -790,7 +790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -798,7 +798,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -806,7 +806,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -814,7 +814,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -825,10 +825,10 @@
         <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>48</v>
       </c>
@@ -836,7 +836,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
@@ -844,7 +844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
@@ -852,7 +852,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>41</v>
       </c>
@@ -866,52 +866,52 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42"/>
     </row>
   </sheetData>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFF6BA5-DDE0-4250-A4B0-54A8D4C42CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D95A075-1C87-44B9-8150-0036DB9F6816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3990" yWindow="3945" windowWidth="17340" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
     <t>J101</t>
   </si>
   <si>
-    <t>O487</t>
+    <t>O488</t>
   </si>
 </sst>
 </file>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D95A075-1C87-44B9-8150-0036DB9F6816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC75E732-1F6A-4209-B250-226812E37891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3990" yWindow="3945" windowWidth="17340" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
     <t>J101</t>
   </si>
   <si>
-    <t>O488</t>
+    <t>O489</t>
   </si>
 </sst>
 </file>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC75E732-1F6A-4209-B250-226812E37891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40753095-DECE-4246-92EC-DBDEDB14D990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="3945" windowWidth="17340" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40753095-DECE-4246-92EC-DBDEDB14D990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1147CB-CF84-4714-8BD2-F070A81C4471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
     <t>J101</t>
   </si>
   <si>
-    <t>O489</t>
+    <t>O486</t>
   </si>
 </sst>
 </file>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1147CB-CF84-4714-8BD2-F070A81C4471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEB63C1-55EC-4227-97A2-ACED5666F4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12345" yWindow="555" windowWidth="13785" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -226,28 +226,28 @@
     <t>coeqwal_GW_scenario_listing_v3.xlsx</t>
   </si>
   <si>
-    <t>A101</t>
-  </si>
-  <si>
-    <t>B101</t>
-  </si>
-  <si>
-    <t>C101</t>
-  </si>
-  <si>
-    <t>G101</t>
-  </si>
-  <si>
-    <t>H101</t>
-  </si>
-  <si>
-    <t>I101</t>
-  </si>
-  <si>
-    <t>J101</t>
-  </si>
-  <si>
-    <t>O486</t>
+    <t>O488</t>
+  </si>
+  <si>
+    <t>A117</t>
+  </si>
+  <si>
+    <t>B117</t>
+  </si>
+  <si>
+    <t>C117</t>
+  </si>
+  <si>
+    <t>G117</t>
+  </si>
+  <si>
+    <t>H117</t>
+  </si>
+  <si>
+    <t>I117</t>
+  </si>
+  <si>
+    <t>J117</t>
   </si>
 </sst>
 </file>
@@ -585,14 +585,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.6640625" customWidth="1"/>
-    <col min="3" max="5" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="5" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -606,7 +606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -614,7 +614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -622,7 +622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -630,7 +630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -641,10 +641,10 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -655,10 +655,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -669,10 +669,10 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -683,10 +683,10 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>61</v>
       </c>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -711,10 +711,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -725,10 +725,10 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -736,7 +736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -744,7 +744,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -752,7 +752,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -766,7 +766,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -774,7 +774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -782,7 +782,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -790,7 +790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -798,7 +798,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -806,7 +806,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -814,7 +814,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -825,10 +825,10 @@
         <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>48</v>
       </c>
@@ -836,7 +836,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
@@ -844,7 +844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
@@ -852,7 +852,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>41</v>
       </c>
@@ -866,52 +866,52 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
   </sheetData>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEB63C1-55EC-4227-97A2-ACED5666F4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EAFCB0-5AD5-4ECD-B573-ECEB6A732F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12345" yWindow="555" windowWidth="13785" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="18540" windowHeight="18645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -220,9 +220,6 @@
     <t>SV Dss path names</t>
   </si>
   <si>
-    <t>E266</t>
-  </si>
-  <si>
     <t>coeqwal_GW_scenario_listing_v3.xlsx</t>
   </si>
   <si>
@@ -248,6 +245,9 @@
   </si>
   <si>
     <t>J117</t>
+  </si>
+  <si>
+    <t>E267</t>
   </si>
 </sst>
 </file>
@@ -619,7 +619,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -641,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -655,7 +655,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -669,7 +669,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -683,7 +683,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -697,7 +697,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -711,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -725,7 +725,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -763,7 +763,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,7 +825,7 @@
         <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EAFCB0-5AD5-4ECD-B573-ECEB6A732F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7706298F-C750-406A-B94D-80807C3E8B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="18540" windowHeight="18645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
     <t>J117</t>
   </si>
   <si>
-    <t>E267</t>
+    <t>E270</t>
   </si>
 </sst>
 </file>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7706298F-C750-406A-B94D-80807C3E8B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F496A58-7A32-4CD7-A49A-666246749E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
     <t>J117</t>
   </si>
   <si>
-    <t>E270</t>
+    <t>E271</t>
   </si>
 </sst>
 </file>

--- a/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3GroundWaterDataExtractionInitFile_v3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F496A58-7A32-4CD7-A49A-666246749E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2EDFBD-0699-465E-9CA7-B1A98539B7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
     <t>J117</t>
   </si>
   <si>
-    <t>E271</t>
+    <t>E270</t>
   </si>
 </sst>
 </file>
